--- a/Input/Leagues 22-to-21.xlsx
+++ b/Input/Leagues 22-to-21.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nady\Documents\GitHub\PES-Master-CompsAndTeam-Grabber\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EC48B3-2646-49E5-9A93-C9C8085D7704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B66307-77AB-4FB0-8411-662DC0899C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13667" xr2:uid="{269B7300-8F4F-443E-A8C4-E0FEB8C2F215}"/>
+    <workbookView xWindow="12463" yWindow="0" windowWidth="12776" windowHeight="13536" xr2:uid="{269B7300-8F4F-443E-A8C4-E0FEB8C2F215}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -339,9 +339,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -379,7 +379,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -485,7 +485,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -627,7 +627,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1190,13 +1190,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B32">
-        <v>694</v>
+        <v>125</v>
       </c>
       <c r="C32" t="s">
         <v>74</v>
       </c>
       <c r="D32">
-        <v>125</v>
+        <v>694</v>
       </c>
     </row>
   </sheetData>

--- a/Input/Leagues 22-to-21.xlsx
+++ b/Input/Leagues 22-to-21.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nady\Documents\GitHub\PES-Master-CompsAndTeam-Grabber\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B66307-77AB-4FB0-8411-662DC0899C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{416FE356-3896-4E5F-814E-F4E7C238C89B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12463" yWindow="0" windowWidth="12776" windowHeight="13536" xr2:uid="{269B7300-8F4F-443E-A8C4-E0FEB8C2F215}"/>
+    <workbookView xWindow="2239" yWindow="0" windowWidth="12567" windowHeight="13431" xr2:uid="{269B7300-8F4F-443E-A8C4-E0FEB8C2F215}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="77">
   <si>
     <t>name21</t>
   </si>
@@ -280,6 +280,12 @@
   </si>
   <si>
     <t>K League</t>
+  </si>
+  <si>
+    <t>AFC2</t>
+  </si>
+  <si>
+    <t>AFC Champions League Elite</t>
   </si>
 </sst>
 </file>
@@ -736,7 +742,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="D3">
         <v>101</v>
@@ -746,6 +752,12 @@
       </c>
       <c r="F3">
         <v>603</v>
+      </c>
+      <c r="G3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3">
+        <v>703</v>
       </c>
       <c r="K3" t="s">
         <v>13</v>
